--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공릉 라이크짐 PT</t>
+          <t>에이블짐 노원역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>likegym88@naver.com</t>
+          <t>ablegym9@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1301-6597</t>
+          <t>0507-1421-9500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울특별시 노원구 동일로 1401 상아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>https://blog.naver.com/ablegym9/224236979092</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>387</v>
+        <v>2844</v>
       </c>
       <c r="Q2" t="n">
-        <v>1679</v>
+        <v>1654</v>
       </c>
       <c r="R2" t="n">
-        <v>2066</v>
+        <v>4498</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1754784084</t>
+          <t>1033654060</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754784084</t>
+          <t>https://m.place.naver.com/place/1033654060</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>버클다운짐 노원점</t>
+          <t>팔로우짐 중계점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jej120506@naver.com</t>
+          <t>followgym3_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1315-3972</t>
+          <t>0507-1396-7040</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+          <t>서울특별시 노원구 덕릉로 459-37 상가동 지하1호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>https://blog.naver.com/followgym3_</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3336</v>
+        <v>195</v>
       </c>
       <c r="Q3" t="n">
-        <v>2737</v>
+        <v>336</v>
       </c>
       <c r="R3" t="n">
-        <v>6073</v>
+        <v>531</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1930996201</t>
+          <t>2074166663</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930996201</t>
+          <t>https://m.place.naver.com/place/2074166663</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>다올핏</t>
+          <t>버클다운짐 노원점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>woodnjsrb@naver.com</t>
+          <t>jej120506@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1347-9068</t>
+          <t>0507-1315-3972</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woodnjsrb/223994512288</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>69</v>
+        <v>3337</v>
       </c>
       <c r="Q4" t="n">
-        <v>538</v>
+        <v>2738</v>
       </c>
       <c r="R4" t="n">
-        <v>607</v>
+        <v>6075</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1207679430</t>
+          <t>1930996201</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207679430</t>
+          <t>https://m.place.naver.com/place/1930996201</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>직선 퍼스널트레이닝</t>
+          <t>공릉 라이크짐 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ziksun001@naver.com</t>
+          <t>likegym88@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1478-9683</t>
+          <t>0507-1301-6597</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>https://blog.naver.com/likegym88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>97</v>
+        <v>388</v>
       </c>
       <c r="Q5" t="n">
-        <v>381</v>
+        <v>1681</v>
       </c>
       <c r="R5" t="n">
-        <v>478</v>
+        <v>2069</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1411508464</t>
+          <t>1754784084</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1411508464</t>
+          <t>https://m.place.naver.com/place/1754784084</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리핏트레이닝센터 PT 노원역점</t>
+          <t>다올핏</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leefitnowon@naver.com</t>
+          <t>woodnjsrb@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1442-5622</t>
+          <t>0507-1347-9068</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 76 B1층</t>
+          <t>서울특별시 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leefitnowon</t>
+          <t>https://blog.naver.com/woodnjsrb/223994512288</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>252</v>
+        <v>69</v>
       </c>
       <c r="Q6" t="n">
-        <v>314</v>
+        <v>534</v>
       </c>
       <c r="R6" t="n">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1399680010</t>
+          <t>1207679430</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399680010</t>
+          <t>https://m.place.naver.com/place/1207679430</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>트로이짐다이어트PT 노원역점</t>
+          <t>직선 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>troygym@naver.com</t>
+          <t>ziksun001@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1327-2093</t>
+          <t>0507-1478-9683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로218길 25 402호</t>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_cfyRn</t>
+          <t>https://blog.naver.com/ziksun001</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="Q7" t="n">
-        <v>165</v>
+        <v>382</v>
       </c>
       <c r="R7" t="n">
-        <v>175</v>
+        <v>479</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1408185308</t>
+          <t>1411508464</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1408185308</t>
+          <t>https://m.place.naver.com/place/1411508464</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,39 +1123,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
+          <t>리핏트레이닝센터 PT 노원역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>winnersboxing@naver.com</t>
+          <t>leefitnowon@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-935-9312</t>
+          <t>0507-1442-5622</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로 680 6층 601호</t>
+          <t>서울특별시 노원구 상계로 76 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@winnersboxing</t>
+          <t>https://blog.naver.com/leefitnowon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,19 +1165,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1gc5eq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="Q8" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="R8" t="n">
-        <v>284</v>
+        <v>566</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>21718297</t>
+          <t>1399680010</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21718297</t>
+          <t>https://m.place.naver.com/place/1399680010</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q9" t="n">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="R9" t="n">
-        <v>3672</v>
+        <v>3675</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1315,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>여성전용 피트니스 미슬 중계클럽</t>
+          <t>바디라인PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>miscle@naver.com</t>
+          <t>bodyline-pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1366-3035</t>
+          <t>0507-1402-8151</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 섬밭로 258 건영옴니백화점 5층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miscle</t>
+          <t>https://blog.naver.com/bodyline-pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1368,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="Q10" t="n">
-        <v>147</v>
+        <v>586</v>
       </c>
       <c r="R10" t="n">
-        <v>171</v>
+        <v>716</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1109750805</t>
+          <t>1914447631</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109750805</t>
+          <t>https://m.place.naver.com/place/1914447631</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1499,6 +1495,100 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>데일리짐 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sarere91@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1393-0882</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 동일로 1649 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sarere91</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>237</v>
+      </c>
+      <c r="R12" t="n">
+        <v>283</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1843525848</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1843525848</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="Q2" t="n">
-        <v>1654</v>
+        <v>1439</v>
       </c>
       <c r="R2" t="n">
-        <v>4498</v>
+        <v>4284</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,41 +646,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>팔로우짐 중계점</t>
+          <t>버클다운짐 노원점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>followgym3_@naver.com</t>
+          <t>jej120506@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1396-7040</t>
+          <t>0507-1315-3972</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 덕릉로 459-37 상가동 지하1호</t>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/followgym3_</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>195</v>
+        <v>3366</v>
       </c>
       <c r="Q3" t="n">
-        <v>336</v>
+        <v>2748</v>
       </c>
       <c r="R3" t="n">
-        <v>531</v>
+        <v>6114</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2074166663</t>
+          <t>1930996201</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074166663</t>
+          <t>https://m.place.naver.com/place/1930996201</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버클다운짐 노원점</t>
+          <t>공릉 라이크짐 PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jej120506@naver.com</t>
+          <t>likegym88@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1315-3972</t>
+          <t>0507-1301-6597</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>https://blog.naver.com/likegym88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3337</v>
+        <v>393</v>
       </c>
       <c r="Q4" t="n">
-        <v>2738</v>
+        <v>1708</v>
       </c>
       <c r="R4" t="n">
-        <v>6075</v>
+        <v>2101</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1930996201</t>
+          <t>1754784084</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930996201</t>
+          <t>https://m.place.naver.com/place/1754784084</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공릉 라이크짐 PT</t>
+          <t>직선 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>likegym88@naver.com</t>
+          <t>ziksun001@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1301-6597</t>
+          <t>0507-1478-9683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>https://blog.naver.com/ziksun001</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q5" t="n">
         <v>388</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1681</v>
-      </c>
       <c r="R5" t="n">
-        <v>2069</v>
+        <v>486</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1754784084</t>
+          <t>1411508464</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754784084</t>
+          <t>https://m.place.naver.com/place/1411508464</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1000,10 +1000,10 @@
         <v>69</v>
       </c>
       <c r="Q6" t="n">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="R6" t="n">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>직선 퍼스널트레이닝</t>
+          <t>일상의운동 PT 노원역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ziksun001@naver.com</t>
+          <t>dailyworkout01@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1478-9683</t>
+          <t>0507-1375-7281</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 상계로 70 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>https://blog.naver.com/dailyworkout01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="Q7" t="n">
-        <v>382</v>
+        <v>174</v>
       </c>
       <c r="R7" t="n">
-        <v>479</v>
+        <v>399</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1411508464</t>
+          <t>1567478488</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1411508464</t>
+          <t>https://m.place.naver.com/place/1567478488</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리핏트레이닝센터 PT 노원역점</t>
+          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>leefitnowon@naver.com</t>
+          <t>winnersboxing@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1442-5622</t>
+          <t>02-935-9312</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 76 B1층</t>
+          <t>서울 노원구 덕릉로 680 6층 601호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leefitnowon</t>
+          <t>https://www.youtube.com/@winnersboxing</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1165,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1gc5eq</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>252</v>
+        <v>35</v>
       </c>
       <c r="Q8" t="n">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="R8" t="n">
-        <v>566</v>
+        <v>289</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1399680010</t>
+          <t>21718297</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399680010</t>
+          <t>https://m.place.naver.com/place/21718297</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>찬스스포츠그라운드</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>chans_sport@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1359-9819</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 한글비석로 460 B1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://blog.naver.com/chans_sport</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1033</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2642</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>3675</v>
+        <v>12</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>2069511927</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/2069511927</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디라인PT</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyline-pt@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-8151</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline-pt</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>130</v>
+        <v>1038</v>
       </c>
       <c r="Q10" t="n">
-        <v>586</v>
+        <v>2656</v>
       </c>
       <c r="R10" t="n">
-        <v>716</v>
+        <v>3694</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1914447631</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914447631</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R11" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1496,101 +1500,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>데일리짐 PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>sarere91@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1393-0882</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 노원구 동일로 1649 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/sarere91</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>237</v>
-      </c>
-      <c r="R12" t="n">
-        <v>283</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1843525848</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1843525848</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 노원역점</t>
+          <t>버클다운짐 노원점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym9@naver.com</t>
+          <t>jej120506@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1421-9500</t>
+          <t>0507-1315-3972</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1401 상아빌딩 지하1층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym9/224236979092</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2845</v>
+        <v>3370</v>
       </c>
       <c r="Q2" t="n">
-        <v>1439</v>
+        <v>2752</v>
       </c>
       <c r="R2" t="n">
-        <v>4284</v>
+        <v>6122</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1033654060</t>
+          <t>1930996201</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033654060</t>
+          <t>https://m.place.naver.com/place/1930996201</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>버클다운짐 노원점</t>
+          <t>공릉 라이크짐 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jej120506@naver.com</t>
+          <t>likegym88@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1315-3972</t>
+          <t>0507-1301-6597</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>https://blog.naver.com/likegym88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3366</v>
+        <v>393</v>
       </c>
       <c r="Q3" t="n">
-        <v>2748</v>
+        <v>1710</v>
       </c>
       <c r="R3" t="n">
-        <v>6114</v>
+        <v>2103</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1930996201</t>
+          <t>1754784084</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930996201</t>
+          <t>https://m.place.naver.com/place/1754784084</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공릉 라이크짐 PT</t>
+          <t>직선 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>likegym88@naver.com</t>
+          <t>ziksun001@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1301-6597</t>
+          <t>0507-1478-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>https://blog.naver.com/ziksun001</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>393</v>
+        <v>98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1708</v>
+        <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>2101</v>
+        <v>486</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1754784084</t>
+          <t>1411508464</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754784084</t>
+          <t>https://m.place.naver.com/place/1411508464</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>직선 퍼스널트레이닝</t>
+          <t>다올핏</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ziksun001@naver.com</t>
+          <t>woodnjsrb@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1478-9683</t>
+          <t>0507-1347-9068</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>https://blog.naver.com/woodnjsrb/223994512288</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="Q5" t="n">
-        <v>388</v>
+        <v>525</v>
       </c>
       <c r="R5" t="n">
-        <v>486</v>
+        <v>594</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1411508464</t>
+          <t>1207679430</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1411508464</t>
+          <t>https://m.place.naver.com/place/1207679430</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>다올핏</t>
+          <t>리핏트레이닝센터 PT 노원역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>woodnjsrb@naver.com</t>
+          <t>leefitnowon@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1347-9068</t>
+          <t>0507-1442-5622</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
+          <t>서울특별시 노원구 상계로 76 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woodnjsrb/223994512288</t>
+          <t>https://blog.naver.com/leefitnowon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>69</v>
+        <v>253</v>
       </c>
       <c r="Q6" t="n">
-        <v>525</v>
+        <v>316</v>
       </c>
       <c r="R6" t="n">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1207679430</t>
+          <t>1399680010</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207679430</t>
+          <t>https://m.place.naver.com/place/1399680010</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>일상의운동 PT 노원역점</t>
+          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dailyworkout01@naver.com</t>
+          <t>winnersboxing@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1375-7281</t>
+          <t>02-935-9312</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 70 4층</t>
+          <t>서울 노원구 덕릉로 680 6층 601호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dailyworkout01</t>
+          <t>https://www.youtube.com/@winnersboxing</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,15 +1071,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1gc5eq</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="n">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="R7" t="n">
-        <v>399</v>
+        <v>290</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1567478488</t>
+          <t>21718297</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1567478488</t>
+          <t>https://m.place.naver.com/place/21718297</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
+          <t>찬스스포츠그라운드</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>winnersboxing@naver.com</t>
+          <t>chans_sport@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-935-9312</t>
+          <t>0507-1359-9819</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로 680 6층 601호</t>
+          <t>서울특별시 노원구 한글비석로 460 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@winnersboxing</t>
+          <t>https://blog.naver.com/chans_sport</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,19 +1169,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1gc5eq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>254</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>289</v>
+        <v>12</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,51 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>21718297</t>
+          <t>2069511927</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21718297</t>
+          <t>https://m.place.naver.com/place/2069511927</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>찬스스포츠그라운드</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chans_sport@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-9819</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 460 B1</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chans_sport</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>1041</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>2663</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>3704</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2069511927</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069511927</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>바디라인PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>bodyline-pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1402-8151</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://blog.naver.com/bodyline-pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1038</v>
+        <v>130</v>
       </c>
       <c r="Q10" t="n">
-        <v>2656</v>
+        <v>586</v>
       </c>
       <c r="R10" t="n">
-        <v>3694</v>
+        <v>716</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>1914447631</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/1914447631</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="47" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+          <t>서울 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4923m</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울 노원구 공릉로51길 14-2 3층 라이크짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q6er</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
+          <t>서울 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44jva</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 76 B1층</t>
+          <t>서울 노원구 상계로 76 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wn1j</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1127,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>찬스스포츠그라운드</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chans_sport@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1359-9819</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 460 B1</t>
+          <t>서울 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chans_sport</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42llu</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>1041</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>2668</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>3709</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2069511927</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069511927</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>secondwind12_nowon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1496-2146</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,15 +1283,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1041</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="n">
-        <v>2663</v>
+        <v>36</v>
       </c>
       <c r="R9" t="n">
-        <v>3704</v>
+        <v>84</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디라인PT</t>
+          <t>데일리짐 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyline-pt@naver.com</t>
+          <t>sarere91@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-8151</t>
+          <t>0507-1393-0882</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+          <t>서울 노원구 동일로 1649 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline-pt</t>
+          <t>https://blog.naver.com/sarere91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnses3n</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>586</v>
+        <v>236</v>
       </c>
       <c r="R10" t="n">
-        <v>716</v>
+        <v>282</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1914447631</t>
+          <t>1843525848</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914447631</t>
+          <t>https://m.place.naver.com/place/1843525848</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>베네핏</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
+          <t>hyeong_seok_moon@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>0507-1477-8279</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울 노원구 동일로 1533 백산빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>https://blog.naver.com/hyeong_seok_moon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1461,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
+          <t>https://talk.naver.com/ct/w4vtqj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1475,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="R11" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1581200562</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1581200562</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 노원구 상계로1길 54-4 2층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4923m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q6er</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -849,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>다올핏</t>
+          <t>스포애니 공릉동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>woodnjsrb@naver.com</t>
+          <t>spoany_57@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1347-9068</t>
+          <t>02-949-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울 노원구 동일로 1689 . 215호(상계동, 하이베라스)</t>
+          <t>서울특별시 노원구 동일로192길 74 B1,2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woodnjsrb/223994512288</t>
+          <t>https://blog.naver.com/spoany_57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44jva</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>69</v>
+        <v>957</v>
       </c>
       <c r="Q5" t="n">
-        <v>525</v>
+        <v>1989</v>
       </c>
       <c r="R5" t="n">
-        <v>594</v>
+        <v>2946</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1207679430</t>
+          <t>1077112071</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207679430</t>
+          <t>https://m.place.naver.com/place/1077112071</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -969,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울 노원구 상계로 76 B1층</t>
+          <t>서울특별시 노원구 상계로 76 B1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wn1j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1077,7 +1061,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1165,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42llu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="Q8" t="n">
         <v>2668</v>
       </c>
       <c r="R8" t="n">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1241,34 +1221,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>베네핏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
+          <t>hyeong_seok_moon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>0507-1477-8279</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>https://blog.naver.com/hyeong_seok_moon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,19 +1263,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="R9" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1581200562</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1581200562</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>데일리짐 PT</t>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sarere91@naver.com</t>
+          <t>secondwind12_nowon@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1393-0882</t>
+          <t>0507-1496-2146</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 노원구 동일로 1649 2층</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sarere91</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1367,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wnses3n</t>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Q10" t="n">
-        <v>236</v>
+        <v>36</v>
       </c>
       <c r="R10" t="n">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1843525848</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843525848</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>데일리짐 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>sarere91@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>0507-1393-0882</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 동일로 1649 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyeong_seok_moon</t>
+          <t>https://blog.naver.com/sarere91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1484,14 +1460,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vtqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="n">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="R11" t="n">
-        <v>110</v>
+        <v>282</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1843525848</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1843525848</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4923m</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="Q2" t="n">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="R2" t="n">
-        <v>6122</v>
+        <v>6124</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q6er</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +726,10 @@
         <v>393</v>
       </c>
       <c r="Q3" t="n">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="R3" t="n">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -868,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_57</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48j3u</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -962,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leefitnowon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +984,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wn1j</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1016,10 @@
         <v>253</v>
       </c>
       <c r="Q6" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R6" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1029,39 +1045,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>winnersboxing@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-935-9312</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로 680 6층 601호</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@winnersboxing</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1081,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1gc5eq</t>
+          <t>https://talk.naver.com/ct/w42llu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1095,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>1042</v>
       </c>
       <c r="Q7" t="n">
-        <v>255</v>
+        <v>2668</v>
       </c>
       <c r="R7" t="n">
-        <v>290</v>
+        <v>3710</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>21718297</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21718297</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>베네핏</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>hyeong_seok_moon@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1477-8279</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,20 +1180,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vtqj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1042</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2668</v>
+        <v>74</v>
       </c>
       <c r="R8" t="n">
-        <v>3710</v>
+        <v>110</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>1581200562</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/1581200562</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>바디라인PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>bodyline-pt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>0507-1402-8151</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyeong_seok_moon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,20 +1278,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpvkezv</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="Q9" t="n">
-        <v>74</v>
+        <v>586</v>
       </c>
       <c r="R9" t="n">
-        <v>110</v>
+        <v>716</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1914447631</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1914447631</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1342,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1440,7 +1464,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sarere91</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,20 +1474,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnses3n</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4923m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -684,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/likegym88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q6er</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -876,7 +868,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany_57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48j3u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -974,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/leefitnowon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wn1j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1038,46 +1022,46 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>winnersboxing@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>02-935-9312</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울 노원구 덕릉로 680 6층 601호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://www.youtube.com/@winnersboxing</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1081,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42llu</t>
+          <t>https://talk.naver.com/ct/w1gc5eq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1042</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="n">
-        <v>2668</v>
+        <v>255</v>
       </c>
       <c r="R7" t="n">
-        <v>3710</v>
+        <v>290</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>21718297</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/21718297</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1148,39 +1132,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>트로이짐다이어트PT 노원역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>troygym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>0507-1327-2093</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 동일로218길 25 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_cfyRn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1190,17 +1174,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vtqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="R8" t="n">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1408185308</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1408185308</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디라인PT</t>
+          <t>찬스스포츠그라운드</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyline-pt@naver.com</t>
+          <t>chans_sport@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1402-8151</t>
+          <t>0507-1359-9819</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+          <t>서울특별시 노원구 한글비석로 460 B1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/chans_sport</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,24 +1258,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpvkezv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>130</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>586</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>716</v>
+        <v>12</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1914447631</t>
+          <t>2069511927</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914447631</t>
+          <t>https://m.place.naver.com/place/2069511927</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,24 +1352,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48</v>
+        <v>1042</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>2672</v>
       </c>
       <c r="R10" t="n">
-        <v>84</v>
+        <v>3714</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>데일리짐 PT</t>
+          <t>바디라인PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sarere91@naver.com</t>
+          <t>bodyline-pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1393-0882</t>
+          <t>0507-1402-8151</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1649 2층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodyline-pt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,24 +1446,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnses3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="Q11" t="n">
-        <v>236</v>
+        <v>586</v>
       </c>
       <c r="R11" t="n">
-        <v>282</v>
+        <v>716</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1843525848</t>
+          <t>1914447631</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843525848</t>
+          <t>https://m.place.naver.com/place/1914447631</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -718,10 +718,10 @@
         <v>393</v>
       </c>
       <c r="Q3" t="n">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="R3" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>957</v>
       </c>
       <c r="Q5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="R5" t="n">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -935,34 +935,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리핏트레이닝센터 PT 노원역점</t>
+          <t>스포애니 상계역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leefitnowon@naver.com</t>
+          <t>spoany79@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1442-5622</t>
+          <t>0507-1390-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로 76 B1층</t>
+          <t>서울특별시 노원구 한글비석로 383 삼창프라자 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leefitnowon</t>
+          <t>https://blog.naver.com/spoany79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>253</v>
+        <v>1201</v>
       </c>
       <c r="Q6" t="n">
-        <v>317</v>
+        <v>1346</v>
       </c>
       <c r="R6" t="n">
-        <v>570</v>
+        <v>2547</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1399680010</t>
+          <t>1282482674</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399680010</t>
+          <t>https://m.place.naver.com/place/1282482674</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1127,39 +1127,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>트로이짐다이어트PT 노원역점</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>troygym@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1327-2093</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로218길 25 402호</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_cfyRn</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>1042</v>
       </c>
       <c r="Q8" t="n">
-        <v>166</v>
+        <v>2674</v>
       </c>
       <c r="R8" t="n">
-        <v>176</v>
+        <v>3716</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1408185308</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1408185308</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1221,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>찬스스포츠그라운드</t>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chans_sport@naver.com</t>
+          <t>secondwind12_nowon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1359-9819</t>
+          <t>0507-1496-2146</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 460 B1</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chans_sport</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,15 +1263,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="R9" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2069511927</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069511927</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,34 +1319,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>데일리짐 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>sarere91@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1393-0882</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 동일로 1649 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://blog.naver.com/sarere91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1042</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2672</v>
+        <v>236</v>
       </c>
       <c r="R10" t="n">
-        <v>3714</v>
+        <v>282</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>1843525848</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/1843525848</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1414,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디라인PT</t>
+          <t>베네핏</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyline-pt@naver.com</t>
+          <t>hyeong_seok_moon@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1402-8151</t>
+          <t>0507-1477-8279</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline-pt</t>
+          <t>https://blog.naver.com/hyeong_seok_moon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>586</v>
+        <v>74</v>
       </c>
       <c r="R11" t="n">
-        <v>716</v>
+        <v>110</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1914447631</t>
+          <t>1581200562</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914447631</t>
+          <t>https://m.place.naver.com/place/1581200562</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4923m</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -624,10 +628,10 @@
         <v>3371</v>
       </c>
       <c r="Q2" t="n">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="R2" t="n">
-        <v>6124</v>
+        <v>6125</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q6er</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +726,10 @@
         <v>393</v>
       </c>
       <c r="Q3" t="n">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="R3" t="n">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -774,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -841,34 +849,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 공릉동점</t>
+          <t>포미짐 여성전용 헬스 PT 공릉점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany_57@naver.com</t>
+          <t>formegym01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02-949-9618</t>
+          <t>0507-1366-4243</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로192길 74 B1,2층</t>
+          <t>서울특별시 노원구 공릉로 172 반야빌딩 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_57</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49xyw</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>957</v>
+        <v>899</v>
       </c>
       <c r="Q5" t="n">
-        <v>1988</v>
+        <v>112</v>
       </c>
       <c r="R5" t="n">
-        <v>2945</v>
+        <v>1011</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1077112071</t>
+          <t>1996116358</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077112071</t>
+          <t>https://m.place.naver.com/place/1996116358</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 상계역점</t>
+          <t>스포애니 공릉동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany79@naver.com</t>
+          <t>spoany_57@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1390-9618</t>
+          <t>02-949-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 383 삼창프라자 지하1층</t>
+          <t>서울특별시 노원구 동일로192길 74 B1,2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany79</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +984,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48j3u</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1201</v>
+        <v>957</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346</v>
+        <v>1993</v>
       </c>
       <c r="R6" t="n">
-        <v>2547</v>
+        <v>2950</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1282482674</t>
+          <t>1077112071</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282482674</t>
+          <t>https://m.place.naver.com/place/1077112071</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1039,7 +1055,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>winnersboxing@naver.com</t>
+          <t>swiss9312@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1056,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@winnersboxing</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,7 +1082,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1127,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>베네핏</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>hyeong_seok_moon@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1477-8279</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,20 +1180,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vtqj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1042</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2674</v>
+        <v>74</v>
       </c>
       <c r="R8" t="n">
-        <v>3716</v>
+        <v>110</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>1581200562</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/1581200562</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1248,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1346,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sarere91</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,20 +1376,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnses3n</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="n">
         <v>236</v>
       </c>
       <c r="R10" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1413,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>필짐 헬스PT 공릉점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>feelgym2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>0507-1358-7920</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 공릉로 198 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyeong_seok_moon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,23 +1474,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45u7a</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>754</v>
       </c>
       <c r="Q11" t="n">
-        <v>74</v>
+        <v>871</v>
       </c>
       <c r="R11" t="n">
-        <v>110</v>
+        <v>1625</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1286800482</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1286800482</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4923m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3371</v>
+        <v>3373</v>
       </c>
       <c r="Q2" t="n">
         <v>2754</v>
       </c>
       <c r="R2" t="n">
-        <v>6125</v>
+        <v>6127</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -684,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/likegym88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4q6er</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -726,10 +718,10 @@
         <v>393</v>
       </c>
       <c r="Q3" t="n">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="R3" t="n">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -782,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ziksun001</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -876,7 +868,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/formegym01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49xyw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="Q5" t="n">
         <v>112</v>
       </c>
       <c r="R5" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -974,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany_57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w48j3u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="Q6" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="R6" t="n">
-        <v>2950</v>
+        <v>2952</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>swiss9312@naver.com</t>
+          <t>secondwind12_nowon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-935-9312</t>
+          <t>0507-1496-2146</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로 680 6층 601호</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1097,7 +1081,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1gc5eq</t>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Q7" t="n">
-        <v>255</v>
+        <v>36</v>
       </c>
       <c r="R7" t="n">
-        <v>290</v>
+        <v>84</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>21718297</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21718297</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>데일리짐 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>sarere91@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>0507-1393-0882</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 동일로 1649 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sarere91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1164,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vtqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="n">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="R8" t="n">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1204,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1843525848</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1843525848</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>베네핏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
+          <t>hyeong_seok_moon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>0507-1477-8279</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/hyeong_seok_moon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,24 +1258,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="R9" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1581200562</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1581200562</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>데일리짐 PT</t>
+          <t>필짐 헬스PT 공릉점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sarere91@naver.com</t>
+          <t>feelgym2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1393-0882</t>
+          <t>0507-1358-7920</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1649 2층</t>
+          <t>서울특별시 노원구 공릉로 198 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/feelgym2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,7 +1352,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1386,17 +1362,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnses3n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47</v>
+        <v>755</v>
       </c>
       <c r="Q10" t="n">
-        <v>236</v>
+        <v>871</v>
       </c>
       <c r="R10" t="n">
-        <v>283</v>
+        <v>1626</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,46 +1392,30 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1843525848</t>
+          <t>1286800482</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843525848</t>
+          <t>https://m.place.naver.com/place/1286800482</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>필짐 헬스PT 공릉점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>feelgym2@naver.com</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1358-7920</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로 198 2층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1484,32 +1440,28 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45u7a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>754</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>871</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1625</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1286800482</t>
+          <t>7499229</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286800482</t>
+          <t>https://m.place.naver.com/place/7499229</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>버클다운짐 노원점</t>
+          <t>에이블짐 노원역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jej120506@naver.com</t>
+          <t>ablegym9@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1315-3972</t>
+          <t>0507-1421-9500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+          <t>서울특별시 노원구 동일로 1401 상아빌딩 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>https://blog.naver.com/ablegym9/224266612314</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3373</v>
+        <v>2848</v>
       </c>
       <c r="Q2" t="n">
-        <v>2754</v>
+        <v>1471</v>
       </c>
       <c r="R2" t="n">
-        <v>6127</v>
+        <v>4319</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1930996201</t>
+          <t>1033654060</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930996201</t>
+          <t>https://m.place.naver.com/place/1033654060</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -718,10 +718,10 @@
         <v>393</v>
       </c>
       <c r="Q3" t="n">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="R3" t="n">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>직선 퍼스널트레이닝</t>
+          <t>버클다운짐 노원점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ziksun001@naver.com</t>
+          <t>jej120506@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1478-9683</t>
+          <t>0507-1315-3972</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>98</v>
+        <v>3374</v>
       </c>
       <c r="Q4" t="n">
-        <v>388</v>
+        <v>2753</v>
       </c>
       <c r="R4" t="n">
-        <v>486</v>
+        <v>6127</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1411508464</t>
+          <t>1930996201</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1411508464</t>
+          <t>https://m.place.naver.com/place/1930996201</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>포미짐 여성전용 헬스 PT 공릉점</t>
+          <t>직선 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>formegym01@naver.com</t>
+          <t>ziksun001@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1366-4243</t>
+          <t>0507-1478-9683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로 172 반야빌딩 5층</t>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/formegym01</t>
+          <t>https://blog.naver.com/ziksun001</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>900</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="n">
-        <v>112</v>
+        <v>388</v>
       </c>
       <c r="R5" t="n">
-        <v>1012</v>
+        <v>486</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1996116358</t>
+          <t>1411508464</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996116358</t>
+          <t>https://m.place.naver.com/place/1411508464</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,34 +935,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 공릉동점</t>
+          <t>포미짐 여성전용 헬스 PT 공릉점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany_57@naver.com</t>
+          <t>formegym01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02-949-9618</t>
+          <t>0507-1366-4243</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로192길 74 B1,2층</t>
+          <t>서울특별시 노원구 공릉로 172 반야빌딩 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_57</t>
+          <t>https://blog.naver.com/formegym01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>958</v>
+        <v>900</v>
       </c>
       <c r="Q6" t="n">
-        <v>1994</v>
+        <v>112</v>
       </c>
       <c r="R6" t="n">
-        <v>2952</v>
+        <v>1012</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1077112071</t>
+          <t>1996116358</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077112071</t>
+          <t>https://m.place.naver.com/place/1996116358</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,39 +1029,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>휘트니스인X필라테스인 마들점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>fitness_in@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>inpakorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>0507-1355-7207</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울특별시 노원구 수락산로 190 지하1층 비101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>https://www.inpakorea.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,22 +1075,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>48</v>
+        <v>2442</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>773</v>
       </c>
       <c r="R7" t="n">
-        <v>84</v>
+        <v>3215</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1857719873</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1857719873</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1127,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>데일리짐 PT</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sarere91@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1393-0882</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1649 2층</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sarere91</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47</v>
+        <v>1045</v>
       </c>
       <c r="Q8" t="n">
-        <v>236</v>
+        <v>2682</v>
       </c>
       <c r="R8" t="n">
-        <v>283</v>
+        <v>3727</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1843525848</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843525848</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1315,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>필짐 헬스PT 공릉점</t>
+          <t>바디라인PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feelgym2@naver.com</t>
+          <t>bodyline-pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1358-7920</t>
+          <t>0507-1402-8151</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로 198 2층</t>
+          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/feelgym2</t>
+          <t>https://blog.naver.com/bodyline-pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>755</v>
+        <v>130</v>
       </c>
       <c r="Q10" t="n">
-        <v>871</v>
+        <v>586</v>
       </c>
       <c r="R10" t="n">
-        <v>1626</v>
+        <v>716</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1286800482</t>
+          <t>1914447631</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286800482</t>
+          <t>https://m.place.naver.com/place/1914447631</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1407,20 +1407,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>secondwind12_nowon@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1496-2146</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1430,7 +1446,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1440,10 +1456,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1451,17 +1471,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,15 +1490,109 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7499229</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7499229</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>여성전용 피트니스 미슬 중계클럽</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>miscle@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1366-3035</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 노원구 섬밭로 258 건영옴니백화점 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/miscle</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>145</v>
+      </c>
+      <c r="R12" t="n">
+        <v>195</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1109750805</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109750805</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 노원역점</t>
+          <t>공릉 라이크짐 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym9@naver.com</t>
+          <t>likegym88@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1421-9500</t>
+          <t>0507-1301-6597</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1401 상아빌딩 지하1층</t>
+          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym9/224266612314</t>
+          <t>https://blog.naver.com/likegym88</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2848</v>
+        <v>393</v>
       </c>
       <c r="Q2" t="n">
-        <v>1471</v>
+        <v>1717</v>
       </c>
       <c r="R2" t="n">
-        <v>4319</v>
+        <v>2110</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1033654060</t>
+          <t>1754784084</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033654060</t>
+          <t>https://m.place.naver.com/place/1754784084</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공릉 라이크짐 PT</t>
+          <t>버클다운짐 노원점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>likegym88@naver.com</t>
+          <t>jej120506@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1301-6597</t>
+          <t>0507-1315-3972</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로51길 14-2 3층 라이크짐</t>
+          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>https://blog.naver.com/jej120506</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>393</v>
+        <v>3376</v>
       </c>
       <c r="Q3" t="n">
-        <v>1717</v>
+        <v>2753</v>
       </c>
       <c r="R3" t="n">
-        <v>2110</v>
+        <v>6129</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1754784084</t>
+          <t>1930996201</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754784084</t>
+          <t>https://m.place.naver.com/place/1930996201</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버클다운짐 노원점</t>
+          <t>직선 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jej120506@naver.com</t>
+          <t>ziksun001@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1315-3972</t>
+          <t>0507-1478-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 2층</t>
+          <t>서울특별시 노원구 노원로1나길 11 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>https://blog.naver.com/ziksun001</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3374</v>
+        <v>98</v>
       </c>
       <c r="Q4" t="n">
-        <v>2753</v>
+        <v>388</v>
       </c>
       <c r="R4" t="n">
-        <v>6127</v>
+        <v>486</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1930996201</t>
+          <t>1411508464</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1930996201</t>
+          <t>https://m.place.naver.com/place/1411508464</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>직선 퍼스널트레이닝</t>
+          <t>포미짐 여성전용 헬스 PT 공릉점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ziksun001@naver.com</t>
+          <t>formegym01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1478-9683</t>
+          <t>0507-1366-4243</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 노원로1나길 11 2층</t>
+          <t>서울특별시 노원구 공릉로 172 반야빌딩 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>https://blog.naver.com/formegym01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>98</v>
+        <v>900</v>
       </c>
       <c r="Q5" t="n">
-        <v>388</v>
+        <v>112</v>
       </c>
       <c r="R5" t="n">
-        <v>486</v>
+        <v>1012</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +918,60 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1411508464</t>
+          <t>1996116358</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1411508464</t>
+          <t>https://m.place.naver.com/place/1996116358</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포미짐 여성전용 헬스 PT 공릉점</t>
+          <t>휘트니스인X필라테스인 마들점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>formegym01@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>fitness_in@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>inpakorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1366-4243</t>
+          <t>0507-1355-7207</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 공릉로 172 반야빌딩 5층</t>
+          <t>서울특별시 노원구 수락산로 190 지하1층 비101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/formegym01</t>
+          <t>https://www.inpakorea.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>2442</v>
       </c>
       <c r="Q6" t="n">
-        <v>112</v>
+        <v>774</v>
       </c>
       <c r="R6" t="n">
-        <v>1012</v>
+        <v>3216</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,60 +1016,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1996116358</t>
+          <t>1857719873</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996116358</t>
+          <t>https://m.place.naver.com/place/1857719873</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스인X필라테스인 마들점</t>
+          <t>위너스복싱PT다이어트복싱체육관 노원점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fitness_in@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>inpakorea@gmail.com</t>
-        </is>
-      </c>
+          <t>winnersboxing@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1355-7207</t>
+          <t>02-935-9312</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 수락산로 190 지하1층 비101호</t>
+          <t>서울 노원구 덕릉로 680 6층 601호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.inpakorea.com/</t>
+          <t>https://www.youtube.com/@winnersboxing</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,18 +1075,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1gc5eq</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2442</v>
+        <v>35</v>
       </c>
       <c r="Q7" t="n">
-        <v>773</v>
+        <v>256</v>
       </c>
       <c r="R7" t="n">
-        <v>3215</v>
+        <v>291</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,51 +1114,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1857719873</t>
+          <t>21718297</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857719873</t>
+          <t>https://m.place.naver.com/place/21718297</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>찬스스포츠그라운드</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>chans_sport@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1359-9819</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울특별시 노원구 한글비석로 460 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://blog.naver.com/chans_sport</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1045</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2682</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>3727</v>
+        <v>12</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,51 +1208,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>2069511927</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/2069511927</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베네핏</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hyeong_seok_moon@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1477-8279</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로 1533 백산빌딩 4층 402호</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyeong_seok_moon</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>1045</v>
       </c>
       <c r="Q9" t="n">
-        <v>74</v>
+        <v>2684</v>
       </c>
       <c r="R9" t="n">
-        <v>110</v>
+        <v>3729</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1302,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1581200562</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581200562</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디라인PT</t>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyline-pt@naver.com</t>
+          <t>secondwind12_nowon@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-8151</t>
+          <t>0507-1496-2146</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 상계로1길 54-4 센트럴 타워 2층 바디라인</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline-pt</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,15 +1361,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="Q10" t="n">
-        <v>586</v>
+        <v>36</v>
       </c>
       <c r="R10" t="n">
-        <v>716</v>
+        <v>84</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,51 +1400,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1914447631</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914447631</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>여성전용 피트니스 미슬 중계클럽</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
+          <t>miscle@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>0507-1366-3035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울특별시 노원구 섬밭로 258 건영옴니백화점 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>https://blog.naver.com/miscle</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,22 +1459,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="R11" t="n">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,111 +1494,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1109750805</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1109750805</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>여성전용 피트니스 미슬 중계클럽</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>miscle@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1366-3035</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울특별시 노원구 섬밭로 258 건영옴니백화점 5층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/miscle</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>145</v>
-      </c>
-      <c r="R12" t="n">
-        <v>195</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1109750805</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1109750805</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/노원_PT.xlsx
+++ b/naver-place-crawler/results_health/노원_PT.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/likegym88</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q6er</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jej120506</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4923m</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -774,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ziksun001</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -868,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/formegym01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,20 +886,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49xyw</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yel3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1004,10 +1020,10 @@
         <v>2442</v>
       </c>
       <c r="Q6" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="R6" t="n">
-        <v>3216</v>
+        <v>3217</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1043,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>winnersboxing@naver.com</t>
+          <t>swiss9312@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1060,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@winnersboxing</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1131,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>찬스스포츠그라운드</t>
+          <t>휘트니스피플 우먼 노원역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chans_sport@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1359-9819</t>
+          <t>02-930-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 한글비석로 460 B1</t>
+          <t>서울특별시 노원구 동일로217가길 11 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chans_sport</t>
+          <t>https://linktr.ee/fitnesspeoplenowon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1178,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42llu</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>1045</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>2687</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>3732</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2069511927</t>
+          <t>1485094589</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2069511927</t>
+          <t>https://m.place.naver.com/place/1485094589</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1225,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스피플 우먼 노원역점</t>
+          <t>세컨드윈드복싱&amp;크로스핏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>secondwind12_nowon@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02-930-3912</t>
+          <t>0507-1496-2146</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 동일로217가길 11 4층</t>
+          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitnesspeoplenowon</t>
+          <t>https://www.instagram.com/secondwind_nowon/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww4lrr9</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1287,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1045</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="n">
-        <v>2684</v>
+        <v>36</v>
       </c>
       <c r="R9" t="n">
-        <v>3729</v>
+        <v>84</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1485094589</t>
+          <t>1628915690</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485094589</t>
+          <t>https://m.place.naver.com/place/1628915690</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1319,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>세컨드윈드복싱&amp;크로스핏</t>
+          <t>여성전용 피트니스 미슬 중계클럽</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>secondwind12_nowon@naver.com</t>
+          <t>miscle@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1496-2146</t>
+          <t>0507-1366-3035</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 노원구 덕릉로82길 19 4층, 5층</t>
+          <t>서울특별시 노원구 섬밭로 258 건영옴니백화점 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/secondwind_nowon/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,7 +1380,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1371,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/ww4lrr9</t>
+          <t>https://talk.naver.com/ct/w4u07s</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1385,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="R10" t="n">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1628915690</t>
+          <t>1109750805</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628915690</t>
+          <t>https://m.place.naver.com/place/1109750805</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1417,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>여성전용 피트니스 미슬 중계클럽</t>
+          <t>데일리짐 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>miscle@naver.com</t>
+          <t>sarere91@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1366-3035</t>
+          <t>0507-1393-0882</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 노원구 섬밭로 258 건영옴니백화점 5층</t>
+          <t>서울특별시 노원구 동일로 1649 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miscle</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,23 +1478,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnses3n</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1479,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="n">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="R11" t="n">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1109750805</t>
+          <t>1843525848</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109750805</t>
+          <t>https://m.place.naver.com/place/1843525848</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
